--- a/prisma/tdes_branch/TDES_Deployment_Evidence_Supplement_v1.0.xlsx
+++ b/prisma/tdes_branch/TDES_Deployment_Evidence_Supplement_v1.0.xlsx
@@ -374,7 +374,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>TDES Deployment-Evidence Supplement — Final Accounting</t>
+          <t>TDES Deployment-Evidence Supplement - Source Accounting</t>
         </is>
       </c>
       <c r="B1" s="6" t="n"/>
@@ -393,10 +393,12 @@
           <t>Academic records reviewed in the executed search</t>
         </is>
       </c>
-      <c r="B3" s="14" t="n">
-        <v>23</v>
-      </c>
-      <c r="C3" s="14" t="n"/>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr"/>
       <c r="D3" s="14" t="inlineStr">
         <is>
           <t>8 main-corpus re-extractions + 15 targeted-search candidates</t>
@@ -409,13 +411,15 @@
           <t>Additional seed-source academic record</t>
         </is>
       </c>
-      <c r="B4" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="14" t="n"/>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr"/>
       <c r="D4" s="14" t="inlineStr">
         <is>
-          <t>Identified during preliminary scoping: Authenticated Delegation and Authorized AI Agents</t>
+          <t>Authenticated Delegation and Authorized AI Agents</t>
         </is>
       </c>
     </row>
@@ -425,25 +429,33 @@
           <t>Total academic items handled</t>
         </is>
       </c>
-      <c r="B5" s="14" t="n">
-        <v>24</v>
-      </c>
-      <c r="C5" s="14" t="n"/>
-      <c r="D5" s="14" t="n"/>
+      <c r="B5" s="14" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr"/>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>23 records reviewed in the executed search + 1 additional seed source</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>Main-corpus studies revisited for RQ4 re-extraction</t>
-        </is>
-      </c>
-      <c r="B6" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="C6" s="14" t="n"/>
+          <t>Main-corpus studies revisited for deployment re-extraction</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr"/>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>No new source count</t>
+          <t>Already counted in the 222-study main corpus; no additive source count</t>
         </is>
       </c>
     </row>
@@ -453,45 +465,51 @@
           <t>Additional academic candidates assessed</t>
         </is>
       </c>
-      <c r="B7" s="14" t="n">
-        <v>16</v>
-      </c>
-      <c r="C7" s="14" t="n"/>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr"/>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>15 targeted-search + 1 preliminary-scoping seed source</t>
+          <t>15 targeted-search + 1 additional seed source</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>Supplementary academic sources selected</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="C8" s="14" t="n"/>
+          <t>Academic candidates not selected</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr"/>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>Selected for RQ4 deployment evidence; reconciled separately against the main search</t>
+          <t>Redundant outside supplementary scope or post-cutoff</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>Academic candidates not selected</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="n">
-        <v>12</v>
-      </c>
-      <c r="C9" s="14" t="n"/>
+          <t>Supplementary academic sources selected</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr"/>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>Redundant, less direct, outside final theme, or post-cutoff</t>
+          <t>All four were identified by the main systematic search and are outside the 222-study main corpus</t>
         </is>
       </c>
     </row>
@@ -501,11 +519,17 @@
           <t>Provider families reviewed</t>
         </is>
       </c>
-      <c r="B10" s="14" t="n">
-        <v>12</v>
-      </c>
-      <c r="C10" s="14" t="n"/>
-      <c r="D10" s="14" t="n"/>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr"/>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>Bounded purposive provider review</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
@@ -513,35 +537,53 @@
           <t>Official deployment-document locators inspected</t>
         </is>
       </c>
-      <c r="B11" s="14" t="n">
-        <v>23</v>
-      </c>
-      <c r="C11" s="14" t="n"/>
-      <c r="D11" s="14" t="n"/>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr"/>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>Official deployment documentation</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>Official deployment documents selected</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="C12" s="14" t="n"/>
-      <c r="D12" s="14" t="n"/>
+          <t>Official deployment documents not selected</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr"/>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>Relevant but not independently informative within the supplementary scope</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>Official deployment documents not selected</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="n">
-        <v>18</v>
-      </c>
-      <c r="C13" s="14" t="n"/>
-      <c r="D13" s="14" t="n"/>
+          <t>Official deployment documents selected</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C13" s="14" t="inlineStr"/>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>Microsoft x2; AWS x2; Anthropic x1</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
@@ -549,13 +591,15 @@
           <t>Total supplementary TDES sources selected</t>
         </is>
       </c>
-      <c r="B14" s="14" t="n">
-        <v>9</v>
-      </c>
-      <c r="C14" s="14" t="n"/>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C14" s="14" t="inlineStr"/>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>4 academic + 5 official; not a core-study count</t>
+          <t>4 academic + 5 official; not a main-corpus study count</t>
         </is>
       </c>
     </row>
@@ -584,7 +628,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>TDES Ref</t>
+          <t>Source ID</t>
         </is>
       </c>
       <c r="B1" s="6" t="inlineStr">
@@ -616,7 +660,7 @@
     <row r="2">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>[235]</t>
+          <t>TDES-ACA-001</t>
         </is>
       </c>
       <c r="B2" s="14" t="inlineStr">
@@ -631,24 +675,24 @@
       </c>
       <c r="D2" s="14" t="inlineStr">
         <is>
-          <t>Identified by main search; reached n=285 baseline; excluded in author-led final adjudication as redundant with a stronger representative</t>
+          <t>Identified by the main systematic search; not retained in the final 222-study main corpus.</t>
         </is>
       </c>
       <c r="E2" s="14" t="inlineStr">
         <is>
-          <t>Selected as supplementary RQ4 deployment evidence</t>
+          <t>Selected for supplementary deployment evidence.</t>
         </is>
       </c>
       <c r="F2" s="14" t="inlineStr">
         <is>
-          <t>Outside final 222-study main corpus; count once as a supplementary academic source</t>
+          <t>Count once as a supplementary academic source outside the final main-corpus study count.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
-          <t>[236]</t>
+          <t>TDES-ACA-002</t>
         </is>
       </c>
       <c r="B3" s="14" t="inlineStr">
@@ -663,24 +707,24 @@
       </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
-          <t>Identified by main search; excluded at title/abstract quality/admissibility gate (TA4-EQ)</t>
+          <t>Identified by the main systematic search; not retained in the final 222-study main corpus.</t>
         </is>
       </c>
       <c r="E3" s="14" t="inlineStr">
         <is>
-          <t>Selected as supplementary RQ4 deployment evidence</t>
+          <t>Selected for supplementary deployment evidence.</t>
         </is>
       </c>
       <c r="F3" s="14" t="inlineStr">
         <is>
-          <t>Outside final 222-study main corpus; count once as a supplementary academic source</t>
+          <t>Count once as a supplementary academic source outside the final main-corpus study count.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="14" t="inlineStr">
         <is>
-          <t>[237]</t>
+          <t>TDES-ACA-003</t>
         </is>
       </c>
       <c r="B4" s="14" t="inlineStr">
@@ -695,24 +739,24 @@
       </c>
       <c r="D4" s="14" t="inlineStr">
         <is>
-          <t>Identified by main search; excluded at title/abstract scope/evidence-role gate (TA3-E07)</t>
+          <t>Identified by the main systematic search; not retained in the final 222-study main corpus.</t>
         </is>
       </c>
       <c r="E4" s="14" t="inlineStr">
         <is>
-          <t>Selected as supplementary RQ4 deployment evidence</t>
+          <t>Selected for supplementary deployment evidence.</t>
         </is>
       </c>
       <c r="F4" s="14" t="inlineStr">
         <is>
-          <t>Outside final 222-study main corpus; count once as a supplementary academic source</t>
+          <t>Count once as a supplementary academic source outside the final main-corpus study count.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>[238]</t>
+          <t>TDES-ACA-004</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
@@ -727,17 +771,17 @@
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>Identified by main search; excluded at title/abstract scope/evidence-role gate (TA3-E07)</t>
+          <t>Identified by the main systematic search; not retained in the final 222-study main corpus.</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>Selected as supplementary RQ4 deployment evidence</t>
+          <t>Selected for supplementary deployment evidence.</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>Outside final 222-study main corpus; count once as a supplementary academic source</t>
+          <t>Count once as a supplementary academic source outside the final main-corpus study count.</t>
         </is>
       </c>
     </row>
@@ -811,13 +855,15 @@
           <t>Academic records reviewed in executed search</t>
         </is>
       </c>
-      <c r="D2" s="14" t="n">
-        <v>23</v>
-      </c>
-      <c r="E2" s="14" t="n"/>
+      <c r="D2" s="14" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="E2" s="14" t="inlineStr"/>
       <c r="F2" s="14" t="inlineStr">
         <is>
-          <t>8 final-main-corpus re-extractions + 15 targeted-search candidates</t>
+          <t>8 main-corpus re-extractions + 15 targeted-search candidates</t>
         </is>
       </c>
     </row>
@@ -837,8 +883,10 @@
           <t>Main-corpus studies revisited</t>
         </is>
       </c>
-      <c r="D3" s="14" t="n">
-        <v>8</v>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="E3" s="14" t="inlineStr">
         <is>
@@ -847,7 +895,7 @@
       </c>
       <c r="F3" s="14" t="inlineStr">
         <is>
-          <t>Already in final main CUA corpus; re-extraction only; no new count</t>
+          <t>Already in main CUA corpus; re-extraction only; no new count</t>
         </is>
       </c>
     </row>
@@ -864,11 +912,13 @@
       </c>
       <c r="C4" s="14" t="inlineStr">
         <is>
-          <t>Additional seed-source academic record</t>
-        </is>
-      </c>
-      <c r="D4" s="14" t="n">
-        <v>15</v>
+          <t>Targeted-search academic candidates</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
       </c>
       <c r="E4" s="14" t="inlineStr">
         <is>
@@ -877,7 +927,7 @@
       </c>
       <c r="F4" s="14" t="inlineStr">
         <is>
-          <t>Authenticated Delegation; identified during preliminary scoping</t>
+          <t>Candidates identified in targeted searches</t>
         </is>
       </c>
     </row>
@@ -894,16 +944,18 @@
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>Additional seed-source candidate</t>
-        </is>
-      </c>
-      <c r="D5" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="14" t="n"/>
+          <t>Additional seed-source academic record</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr"/>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>[237] Authenticated Delegation; identified during preliminary seed phase</t>
+          <t>Authenticated Delegation and Authorized AI Agents</t>
         </is>
       </c>
     </row>
@@ -923,8 +975,10 @@
           <t>Additional academic candidates assessed</t>
         </is>
       </c>
-      <c r="D6" s="14" t="n">
-        <v>16</v>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
@@ -933,7 +987,7 @@
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>15 targeted-search candidates + 1 preliminary-scoping seed source</t>
+          <t>15 targeted-search candidates + 1 seed source</t>
         </is>
       </c>
     </row>
@@ -950,11 +1004,13 @@
       </c>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>Not selected</t>
-        </is>
-      </c>
-      <c r="D7" s="14" t="n">
-        <v>12</v>
+          <t>Academic candidates not selected</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
@@ -963,7 +1019,7 @@
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>Chapter-fit/nonredundancy, weaker directness, outside final theme, or post-cutoff</t>
+          <t>Redundant, outside supplementary scope, or post-cutoff</t>
         </is>
       </c>
     </row>
@@ -983,8 +1039,10 @@
           <t>Supplementary academic sources selected</t>
         </is>
       </c>
-      <c r="D8" s="14" t="n">
-        <v>4</v>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
@@ -993,7 +1051,7 @@
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>[235]–[238]</t>
+          <t>TDES-ACA-001 through TDES-ACA-004</t>
         </is>
       </c>
     </row>
@@ -1013,13 +1071,15 @@
           <t>Provider families reviewed</t>
         </is>
       </c>
-      <c r="D9" s="14" t="n">
-        <v>12</v>
-      </c>
-      <c r="E9" s="14" t="n"/>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr"/>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>Bounded purposive provider audit</t>
+          <t>Bounded purposive provider review</t>
         </is>
       </c>
     </row>
@@ -1039,8 +1099,10 @@
           <t>Official deployment documents inspected</t>
         </is>
       </c>
-      <c r="D10" s="14" t="n">
-        <v>23</v>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
@@ -1069,8 +1131,10 @@
           <t>Official documents not selected</t>
         </is>
       </c>
-      <c r="D11" s="14" t="n">
-        <v>18</v>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
@@ -1079,7 +1143,7 @@
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>Relevant but redundant/less directly aligned</t>
+          <t>Relevant but not independently informative within the supplementary scope</t>
         </is>
       </c>
     </row>
@@ -1096,11 +1160,13 @@
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>Official documents retained</t>
-        </is>
-      </c>
-      <c r="D12" s="14" t="n">
-        <v>5</v>
+          <t>Official documents selected</t>
+        </is>
+      </c>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
@@ -1109,7 +1175,7 @@
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>[239]–[243]</t>
+          <t>TDES-OFF-001 through TDES-OFF-005</t>
         </is>
       </c>
     </row>
@@ -1129,8 +1195,10 @@
           <t>Supplementary TDES sources selected</t>
         </is>
       </c>
-      <c r="D13" s="14" t="n">
-        <v>9</v>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
@@ -1156,11 +1224,13 @@
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>Selected academic sources for main-search reconciliation</t>
-        </is>
-      </c>
-      <c r="D14" s="14" t="n">
-        <v>4</v>
+          <t>Selected academic sources reconciled to main search</t>
+        </is>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
         <is>
@@ -1169,7 +1239,7 @@
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>Count once if independently present in main PRISMA</t>
+          <t>Outside the 222-study main-corpus denominator</t>
         </is>
       </c>
     </row>
@@ -1189,8 +1259,10 @@
           <t>Official documents outside main-corpus denominator</t>
         </is>
       </c>
-      <c r="D15" s="14" t="n">
-        <v>5</v>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
         <is>
@@ -1199,7 +1271,7 @@
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>Authoritative deployment evidence only</t>
+          <t>Source-reported deployment evidence only</t>
         </is>
       </c>
     </row>
@@ -1249,7 +1321,7 @@
       </c>
       <c r="E1" s="6" t="inlineStr">
         <is>
-          <t>RQ4 domain</t>
+          <t>Deployment domain</t>
         </is>
       </c>
       <c r="F1" s="6" t="inlineStr">
@@ -1291,7 +1363,7 @@
       </c>
       <c r="F2" s="14" t="inlineStr">
         <is>
-          <t>Re-extract only; already represented in the final main CUA corpus</t>
+          <t>Re-extract only; already represented in the main CUA corpus</t>
         </is>
       </c>
       <c r="G2" s="14" t="inlineStr">
@@ -1328,7 +1400,7 @@
       </c>
       <c r="F3" s="14" t="inlineStr">
         <is>
-          <t>Re-extract only; already represented in the final main CUA corpus</t>
+          <t>Re-extract only; already represented in the main CUA corpus</t>
         </is>
       </c>
       <c r="G3" s="14" t="inlineStr">
@@ -1365,7 +1437,7 @@
       </c>
       <c r="F4" s="14" t="inlineStr">
         <is>
-          <t>Re-extract only; already represented in the final main CUA corpus</t>
+          <t>Re-extract only; already represented in the main CUA corpus</t>
         </is>
       </c>
       <c r="G4" s="14" t="inlineStr">
@@ -1402,7 +1474,7 @@
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>Re-extract only; already represented in the final main CUA corpus</t>
+          <t>Re-extract only; already represented in the main CUA corpus</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
@@ -1439,7 +1511,7 @@
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>Re-extract only; already represented in the final main CUA corpus</t>
+          <t>Re-extract only; already represented in the main CUA corpus</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -1476,7 +1548,7 @@
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>Re-extract only; already represented in the final main CUA corpus</t>
+          <t>Re-extract only; already represented in the main CUA corpus</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
@@ -1513,7 +1585,7 @@
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>Re-extract only; already represented in the final main CUA corpus</t>
+          <t>Re-extract only; already represented in the main CUA corpus</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -1550,7 +1622,7 @@
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>Re-extract only; already represented in the final main CUA corpus</t>
+          <t>Re-extract only; already represented in the main CUA corpus</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -1633,7 +1705,7 @@
       </c>
       <c r="J1" s="6" t="inlineStr">
         <is>
-          <t>Temp ref</t>
+          <t>Source ID</t>
         </is>
       </c>
     </row>
@@ -1655,7 +1727,7 @@
       </c>
       <c r="D2" s="14" t="inlineStr">
         <is>
-          <t>formal targeted search</t>
+          <t>targeted search</t>
         </is>
       </c>
       <c r="E2" s="14" t="inlineStr">
@@ -1675,7 +1747,7 @@
       </c>
       <c r="H2" s="14" t="inlineStr">
         <is>
-          <t>Direct CUA human-oversight evidence, but final Section 5 already has direct CUA human evidence [22,162] plus selected adjacent practice evidence [238]; not needed as an additional chapter-specific citation.</t>
+          <t>Relevant human-oversight evidence that adds no independent deployment condition beyond retained sources.</t>
         </is>
       </c>
       <c r="I2" s="14" t="inlineStr">
@@ -1683,7 +1755,7 @@
           <t>https://arxiv.org/abs/2602.16844</t>
         </is>
       </c>
-      <c r="J2" s="14" t="n"/>
+      <c r="J2" s="14" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
@@ -1703,7 +1775,7 @@
       </c>
       <c r="D3" s="14" t="inlineStr">
         <is>
-          <t>formal targeted search</t>
+          <t>targeted search</t>
         </is>
       </c>
       <c r="E3" s="14" t="inlineStr">
@@ -1723,7 +1795,7 @@
       </c>
       <c r="H3" s="14" t="inlineStr">
         <is>
-          <t>Relevant to security–utility tradeoffs, but no distinct final Section 5 claim required this additional citation.</t>
+          <t>Relevant security-utility evidence that adds no independent deployment condition beyond retained sources.</t>
         </is>
       </c>
       <c r="I3" s="14" t="inlineStr">
@@ -1731,7 +1803,7 @@
           <t>https://arxiv.org/abs/2601.12822</t>
         </is>
       </c>
-      <c r="J3" s="14" t="n"/>
+      <c r="J3" s="14" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="14" t="inlineStr">
@@ -1751,7 +1823,7 @@
       </c>
       <c r="D4" s="14" t="inlineStr">
         <is>
-          <t>formal targeted search</t>
+          <t>targeted search</t>
         </is>
       </c>
       <c r="E4" s="14" t="inlineStr">
@@ -1771,7 +1843,7 @@
       </c>
       <c r="H4" s="14" t="inlineStr">
         <is>
-          <t>Relevant isolation evidence, but the final execution-boundary argument is already supported by existing-core system evidence plus retained AWS/Anthropic documentation.</t>
+          <t>Relevant isolation evidence that adds no independent deployment condition beyond retained sources.</t>
         </is>
       </c>
       <c r="I4" s="14" t="inlineStr">
@@ -1779,7 +1851,7 @@
           <t>https://arxiv.org/abs/2605.06393</t>
         </is>
       </c>
-      <c r="J4" s="14" t="n"/>
+      <c r="J4" s="14" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
@@ -1799,7 +1871,7 @@
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>formal targeted search</t>
+          <t>targeted search</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -1819,7 +1891,7 @@
       </c>
       <c r="H5" s="14" t="inlineStr">
         <is>
-          <t>Relevant to authentication deployment, but the final credential argument is more directly served by [237] and retained provider documentation.</t>
+          <t>Relevant authentication evidence that adds no independent deployment condition beyond retained sources.</t>
         </is>
       </c>
       <c r="I5" s="14" t="inlineStr">
@@ -1827,7 +1899,7 @@
           <t>https://arxiv.org/abs/2605.22333</t>
         </is>
       </c>
-      <c r="J5" s="14" t="n"/>
+      <c r="J5" s="14" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
@@ -1847,7 +1919,7 @@
       </c>
       <c r="D6" s="14" t="inlineStr">
         <is>
-          <t>formal targeted search</t>
+          <t>targeted search</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
@@ -1862,12 +1934,12 @@
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
-          <t>CHAPTER_FIT_NONREDUNDANT</t>
+          <t>NONREDUNDANT_EVIDENCE</t>
         </is>
       </c>
       <c r="H6" s="14" t="inlineStr">
         <is>
-          <t>Directly supports the selected credential-custody/supply-chain argument with non-redundant empirical evidence.</t>
+          <t>Provides source-native evidence on credential custody and skill supply chains.</t>
         </is>
       </c>
       <c r="I6" s="14" t="inlineStr">
@@ -1877,7 +1949,7 @@
       </c>
       <c r="J6" s="14" t="inlineStr">
         <is>
-          <t>[235]</t>
+          <t>TDES-ACA-001</t>
         </is>
       </c>
     </row>
@@ -1899,7 +1971,7 @@
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>formal targeted search</t>
+          <t>targeted search</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -1919,7 +1991,7 @@
       </c>
       <c r="H7" s="14" t="inlineStr">
         <is>
-          <t>Relevant ecosystem evidence, but overlaps [235]/[236] without adding a distinct claim used in the final Section 5 synthesis.</t>
+          <t>Relevant ecosystem evidence that overlaps retained credential-leakage and dependency-risk evidence.</t>
         </is>
       </c>
       <c r="I7" s="14" t="inlineStr">
@@ -1927,7 +1999,7 @@
           <t>https://arxiv.org/abs/2602.06547</t>
         </is>
       </c>
-      <c r="J7" s="14" t="n"/>
+      <c r="J7" s="14" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
@@ -1947,7 +2019,7 @@
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>formal targeted search</t>
+          <t>targeted search</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
@@ -1962,12 +2034,12 @@
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>CHAPTER_FIT_NONREDUNDANT</t>
+          <t>NONREDUNDANT_EVIDENCE</t>
         </is>
       </c>
       <c r="H8" s="14" t="inlineStr">
         <is>
-          <t>Directly supports the selected transitive-dependency/supply-chain-boundary argument and adds a distinct evidence function beyond credential leakage.</t>
+          <t>Provides source-native evidence on transitive dependencies and supply-chain boundaries.</t>
         </is>
       </c>
       <c r="I8" s="14" t="inlineStr">
@@ -1977,7 +2049,7 @@
       </c>
       <c r="J8" s="14" t="inlineStr">
         <is>
-          <t>[236]</t>
+          <t>TDES-ACA-002</t>
         </is>
       </c>
     </row>
@@ -1999,7 +2071,7 @@
       </c>
       <c r="D9" s="14" t="inlineStr">
         <is>
-          <t>formal targeted search</t>
+          <t>targeted search</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
@@ -2014,12 +2086,12 @@
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>OUTSIDE_FINAL_THEME</t>
+          <t>OUTSIDE_SUPPLEMENT_SCOPE</t>
         </is>
       </c>
       <c r="H9" s="14" t="inlineStr">
         <is>
-          <t>Registry discovery/ranking manipulation is relevant but outside the final selected deployment-condition claims.</t>
+          <t>Relevant registry-governance evidence outside the defined supplementary deployment-evidence scope.</t>
         </is>
       </c>
       <c r="I9" s="14" t="inlineStr">
@@ -2027,7 +2099,7 @@
           <t>https://arxiv.org/abs/2605.11418</t>
         </is>
       </c>
-      <c r="J9" s="14" t="n"/>
+      <c r="J9" s="14" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
@@ -2047,7 +2119,7 @@
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>formal targeted search</t>
+          <t>targeted search</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
@@ -2067,7 +2139,7 @@
       </c>
       <c r="H10" s="14" t="inlineStr">
         <is>
-          <t>Broader vulnerability measurement is redundant with [235]/[236] for the final chapter purpose.</t>
+          <t>Relevant vulnerability-measurement evidence that overlaps retained credential-leakage and dependency-risk evidence.</t>
         </is>
       </c>
       <c r="I10" s="14" t="inlineStr">
@@ -2075,7 +2147,7 @@
           <t>https://arxiv.org/abs/2601.10338</t>
         </is>
       </c>
-      <c r="J10" s="14" t="n"/>
+      <c r="J10" s="14" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
@@ -2095,7 +2167,7 @@
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>formal targeted search</t>
+          <t>targeted search</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
@@ -2110,12 +2182,12 @@
       </c>
       <c r="G11" s="14" t="inlineStr">
         <is>
-          <t>CHAPTER_FIT_NONREDUNDANT</t>
+          <t>NONREDUNDANT_EVIDENCE</t>
         </is>
       </c>
       <c r="H11" s="14" t="inlineStr">
         <is>
-          <t>Directly supports the selected oversight-work taxonomy and complements existing direct-CUA human evidence without duplicating it.</t>
+          <t>Provides source-native evidence on oversight work and developer workflow practice.</t>
         </is>
       </c>
       <c r="I11" s="14" t="inlineStr">
@@ -2125,7 +2197,7 @@
       </c>
       <c r="J11" s="14" t="inlineStr">
         <is>
-          <t>[238]</t>
+          <t>TDES-ACA-004</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2219,7 @@
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>formal targeted search</t>
+          <t>targeted search</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
@@ -2167,7 +2239,7 @@
       </c>
       <c r="H12" s="14" t="inlineStr">
         <is>
-          <t>Useful adjacent approval-integrity evidence, but existing direct-CUA evidence + [238]/[240] are more directly aligned.</t>
+          <t>Relevant consent-integrity evidence that adds no independent deployment condition beyond retained sources.</t>
         </is>
       </c>
       <c r="I12" s="14" t="inlineStr">
@@ -2175,7 +2247,7 @@
           <t>https://arxiv.org/abs/2606.02668</t>
         </is>
       </c>
-      <c r="J12" s="14" t="n"/>
+      <c r="J12" s="14" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
@@ -2195,7 +2267,7 @@
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
-          <t>formal targeted search</t>
+          <t>targeted search</t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
@@ -2210,12 +2282,12 @@
       </c>
       <c r="G13" s="14" t="inlineStr">
         <is>
-          <t>OUTSIDE_FINAL_THEME</t>
+          <t>OUTSIDE_SUPPLEMENT_SCOPE</t>
         </is>
       </c>
       <c r="H13" s="14" t="inlineStr">
         <is>
-          <t>Model-based oversight-capacity evidence is more indirect than retained human or official deployment-document evidence and not required for the chapter's final empirical claims.</t>
+          <t>Relevant oversight-capacity evidence outside the defined supplementary deployment-evidence scope.</t>
         </is>
       </c>
       <c r="I13" s="14" t="inlineStr">
@@ -2223,7 +2295,7 @@
           <t>https://arxiv.org/abs/2606.08919</t>
         </is>
       </c>
-      <c r="J13" s="14" t="n"/>
+      <c r="J13" s="14" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
@@ -2243,7 +2315,7 @@
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>formal targeted search</t>
+          <t>targeted search</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
@@ -2258,12 +2330,12 @@
       </c>
       <c r="G14" s="14" t="inlineStr">
         <is>
-          <t>OUTSIDE_FINAL_THEME</t>
+          <t>OUTSIDE_SUPPLEMENT_SCOPE</t>
         </is>
       </c>
       <c r="H14" s="14" t="inlineStr">
         <is>
-          <t>General-agent incident-response evidence is adjacent to CUA; final recovery synthesis remains anchored to existing CUA evidence.</t>
+          <t>Relevant incident-response evidence outside the defined supplementary deployment-evidence scope.</t>
         </is>
       </c>
       <c r="I14" s="14" t="inlineStr">
@@ -2271,7 +2343,7 @@
           <t>https://arxiv.org/abs/2602.11749</t>
         </is>
       </c>
-      <c r="J14" s="14" t="n"/>
+      <c r="J14" s="14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -2291,7 +2363,7 @@
       </c>
       <c r="D15" s="14" t="inlineStr">
         <is>
-          <t>formal targeted search</t>
+          <t>targeted search</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
@@ -2306,12 +2378,12 @@
       </c>
       <c r="G15" s="14" t="inlineStr">
         <is>
-          <t>OUTSIDE_FINAL_THEME</t>
+          <t>OUTSIDE_SUPPLEMENT_SCOPE</t>
         </is>
       </c>
       <c r="H15" s="14" t="inlineStr">
         <is>
-          <t>Useful rollback semantics, but not needed for the final CUA deployment-condition argument.</t>
+          <t>Relevant rollback-semantics evidence outside the defined supplementary deployment-evidence scope.</t>
         </is>
       </c>
       <c r="I15" s="14" t="inlineStr">
@@ -2319,7 +2391,7 @@
           <t>https://arxiv.org/abs/2603.20625</t>
         </is>
       </c>
-      <c r="J15" s="14" t="n"/>
+      <c r="J15" s="14" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
@@ -2339,7 +2411,7 @@
       </c>
       <c r="D16" s="14" t="inlineStr">
         <is>
-          <t>formal targeted search</t>
+          <t>targeted search</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
@@ -2359,7 +2431,7 @@
       </c>
       <c r="H16" s="14" t="inlineStr">
         <is>
-          <t>Post-cutoff and not required for the final chapter-specific supplement.</t>
+          <t>Published after the review cutoff used for the supplementary route.</t>
         </is>
       </c>
       <c r="I16" s="14" t="inlineStr">
@@ -2367,7 +2439,7 @@
           <t>https://arxiv.org/abs/2608.10502</t>
         </is>
       </c>
-      <c r="J16" s="14" t="n"/>
+      <c r="J16" s="14" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
@@ -2387,7 +2459,7 @@
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
-          <t>preliminary scoping seed route</t>
+          <t>targeted seed route</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">
@@ -2402,12 +2474,12 @@
       </c>
       <c r="G17" s="14" t="inlineStr">
         <is>
-          <t>CHAPTER_FIT_NONREDUNDANT</t>
+          <t>NONREDUNDANT_EVIDENCE</t>
         </is>
       </c>
       <c r="H17" s="14" t="inlineStr">
         <is>
-          <t>Directly supports the selected argument on agent-specific credentials, delegated authority, OAuth/OIDC, and scope; retained after full-text verification.</t>
+          <t>Provides source-native evidence on agent-specific credentials delegated authority OAuth/OIDC and scope.</t>
         </is>
       </c>
       <c r="I17" s="14" t="inlineStr">
@@ -2417,7 +2489,7 @@
       </c>
       <c r="J17" s="14" t="inlineStr">
         <is>
-          <t>[237]</t>
+          <t>TDES-ACA-003</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2570,7 @@
       </c>
       <c r="E2" s="14" t="inlineStr">
         <is>
-          <t>Direct CUA human-oversight evidence, but final Section 5 already has direct CUA human evidence [22,162] plus selected adjacent practice evidence [238]; not needed as an additional chapter-specific citation.</t>
+          <t>Relevant human-oversight evidence that adds no independent deployment condition beyond retained sources.</t>
         </is>
       </c>
       <c r="F2" s="14" t="inlineStr">
@@ -2530,7 +2602,7 @@
       </c>
       <c r="E3" s="14" t="inlineStr">
         <is>
-          <t>Relevant to security–utility tradeoffs, but no distinct final Section 5 claim required this additional citation.</t>
+          <t>Relevant security-utility evidence that adds no independent deployment condition beyond retained sources.</t>
         </is>
       </c>
       <c r="F3" s="14" t="inlineStr">
@@ -2562,7 +2634,7 @@
       </c>
       <c r="E4" s="14" t="inlineStr">
         <is>
-          <t>Relevant isolation evidence, but the final execution-boundary argument is already supported by existing-core system evidence plus retained AWS/Anthropic documentation.</t>
+          <t>Relevant isolation evidence that adds no independent deployment condition beyond retained sources.</t>
         </is>
       </c>
       <c r="F4" s="14" t="inlineStr">
@@ -2594,7 +2666,7 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>Relevant to authentication deployment, but the final credential argument is more directly served by [237] and retained provider documentation.</t>
+          <t>Relevant authentication evidence that adds no independent deployment condition beyond retained sources.</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
@@ -2626,7 +2698,7 @@
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>Relevant ecosystem evidence, but overlaps [235]/[236] without adding a distinct claim used in the final Section 5 synthesis.</t>
+          <t>Relevant ecosystem evidence that overlaps retained credential-leakage and dependency-risk evidence.</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
@@ -2653,12 +2725,12 @@
       </c>
       <c r="D7" s="14" t="inlineStr">
         <is>
-          <t>OUTSIDE_FINAL_THEME</t>
+          <t>OUTSIDE_SUPPLEMENT_SCOPE</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>Registry discovery/ranking manipulation is relevant but outside the final selected deployment-condition claims.</t>
+          <t>Relevant registry-governance evidence outside the defined supplementary deployment-evidence scope.</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
@@ -2690,7 +2762,7 @@
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>Broader vulnerability measurement is redundant with [235]/[236] for the final chapter purpose.</t>
+          <t>Relevant vulnerability-measurement evidence that overlaps retained credential-leakage and dependency-risk evidence.</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
@@ -2722,7 +2794,7 @@
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>Useful adjacent approval-integrity evidence, but existing direct-CUA evidence + [238]/[240] are more directly aligned.</t>
+          <t>Relevant consent-integrity evidence that adds no independent deployment condition beyond retained sources.</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
@@ -2749,12 +2821,12 @@
       </c>
       <c r="D10" s="14" t="inlineStr">
         <is>
-          <t>OUTSIDE_FINAL_THEME</t>
+          <t>OUTSIDE_SUPPLEMENT_SCOPE</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Model-based oversight-capacity evidence is more indirect than retained human or official deployment-document evidence and not required for the chapter's final empirical claims.</t>
+          <t>Relevant oversight-capacity evidence outside the defined supplementary deployment-evidence scope.</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
@@ -2781,12 +2853,12 @@
       </c>
       <c r="D11" s="14" t="inlineStr">
         <is>
-          <t>OUTSIDE_FINAL_THEME</t>
+          <t>OUTSIDE_SUPPLEMENT_SCOPE</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
         <is>
-          <t>General-agent incident-response evidence is adjacent to CUA; final recovery synthesis remains anchored to existing CUA evidence.</t>
+          <t>Relevant incident-response evidence outside the defined supplementary deployment-evidence scope.</t>
         </is>
       </c>
       <c r="F11" s="14" t="inlineStr">
@@ -2813,12 +2885,12 @@
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>OUTSIDE_FINAL_THEME</t>
+          <t>OUTSIDE_SUPPLEMENT_SCOPE</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
         <is>
-          <t>Useful rollback semantics, but not needed for the final CUA deployment-condition argument.</t>
+          <t>Relevant rollback-semantics evidence outside the defined supplementary deployment-evidence scope.</t>
         </is>
       </c>
       <c r="F12" s="14" t="inlineStr">
@@ -2850,7 +2922,7 @@
       </c>
       <c r="E13" s="14" t="inlineStr">
         <is>
-          <t>Post-cutoff and not required for the final chapter-specific supplement.</t>
+          <t>Published after the review cutoff used for the supplementary route.</t>
         </is>
       </c>
       <c r="F13" s="14" t="inlineStr">
@@ -2915,7 +2987,7 @@
       </c>
       <c r="G1" s="6" t="inlineStr">
         <is>
-          <t>Temp ref</t>
+          <t>Source ID</t>
         </is>
       </c>
     </row>
@@ -2947,10 +3019,10 @@
       </c>
       <c r="F2" s="14" t="inlineStr">
         <is>
-          <t>Relevant configuration evidence, but not required by the final Section 5 claims once the selected providers were sufficient.</t>
-        </is>
-      </c>
-      <c r="G2" s="14" t="n"/>
+          <t>Relevant configuration evidence that adds provider breadth without an independent deployment condition.</t>
+        </is>
+      </c>
+      <c r="G2" s="14" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
@@ -2980,10 +3052,10 @@
       </c>
       <c r="F3" s="14" t="inlineStr">
         <is>
-          <t>Relevant configuration evidence, but not required by the final Section 5 claims once the selected providers were sufficient.</t>
-        </is>
-      </c>
-      <c r="G3" s="14" t="n"/>
+          <t>Relevant configuration evidence that adds provider breadth without an independent deployment condition.</t>
+        </is>
+      </c>
+      <c r="G3" s="14" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="14" t="inlineStr">
@@ -3008,17 +3080,17 @@
       </c>
       <c r="E4" s="14" t="inlineStr">
         <is>
-          <t>CHAPTER_FIT_NONREDUNDANT</t>
+          <t>NONREDUNDANT_EVIDENCE</t>
         </is>
       </c>
       <c r="F4" s="14" t="inlineStr">
         <is>
-          <t>Directly supports the selected sandbox/approval-burden argument and provides source-reported operational evidence.</t>
+          <t>Documents sandboxing and approval-burden tradeoffs.</t>
         </is>
       </c>
       <c r="G4" s="14" t="inlineStr">
         <is>
-          <t>[243]</t>
+          <t>TDES-OFF-005</t>
         </is>
       </c>
     </row>
@@ -3045,17 +3117,17 @@
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>CHAPTER_FIT_NONREDUNDANT</t>
+          <t>NONREDUNDANT_EVIDENCE</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>Directly supports maker-provided versus end-user credential semantics in the deployed computer-use setting.</t>
+          <t>Documents credential semantics in a deployed computer-use setting.</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
         <is>
-          <t>[239]</t>
+          <t>TDES-OFF-001</t>
         </is>
       </c>
     </row>
@@ -3082,17 +3154,17 @@
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>CHAPTER_FIT_NONREDUNDANT</t>
+          <t>NONREDUNDANT_EVIDENCE</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>Directly supports the selected human-supervision trigger/reliability argument.</t>
+          <t>Documents human-supervision triggers and reliability conditions.</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
         <is>
-          <t>[240]</t>
+          <t>TDES-OFF-002</t>
         </is>
       </c>
     </row>
@@ -3119,17 +3191,17 @@
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>CHAPTER_FIT_NONREDUNDANT</t>
+          <t>NONREDUNDANT_EVIDENCE</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>Directly supports the selected user-delegated/autonomous credential and microVM execution-boundary argument.</t>
+          <t>Documents delegated and autonomous credential handling and the microVM execution boundary.</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
         <is>
-          <t>[241]</t>
+          <t>TDES-OFF-003</t>
         </is>
       </c>
     </row>
@@ -3156,17 +3228,17 @@
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>CHAPTER_FIT_NONREDUNDANT</t>
+          <t>NONREDUNDANT_EVIDENCE</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>Directly supports credential exposure/management inside the runtime boundary.</t>
+          <t>Documents credential exposure and management inside a runtime boundary.</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
         <is>
-          <t>[242]</t>
+          <t>TDES-OFF-004</t>
         </is>
       </c>
     </row>
@@ -3198,10 +3270,10 @@
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>Relevant identity evidence, but adds breadth rather than a distinct claim needed by the final subsection.</t>
-        </is>
-      </c>
-      <c r="G9" s="14" t="n"/>
+          <t>Relevant identity evidence that adds provider breadth without an independent deployment condition.</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
@@ -3231,10 +3303,10 @@
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>Relevant platform evidence, but adds breadth rather than a distinct claim needed by the final subsection.</t>
-        </is>
-      </c>
-      <c r="G10" s="14" t="n"/>
+          <t>Relevant platform evidence that adds provider breadth without an independent deployment condition.</t>
+        </is>
+      </c>
+      <c r="G10" s="14" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
@@ -3264,10 +3336,10 @@
       </c>
       <c r="F11" s="14" t="inlineStr">
         <is>
-          <t>Relevant confirmation evidence, but redundant with retained supervision/approval sources.</t>
-        </is>
-      </c>
-      <c r="G11" s="14" t="n"/>
+          <t>Relevant confirmation evidence that adds provider breadth without an independent deployment condition.</t>
+        </is>
+      </c>
+      <c r="G11" s="14" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
@@ -3297,10 +3369,10 @@
       </c>
       <c r="F12" s="14" t="inlineStr">
         <is>
-          <t>Relevant authentication evidence, but not needed for the final credential/permission claims.</t>
-        </is>
-      </c>
-      <c r="G12" s="14" t="n"/>
+          <t>Relevant authentication evidence that adds provider breadth without an independent deployment condition.</t>
+        </is>
+      </c>
+      <c r="G12" s="14" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
@@ -3310,7 +3382,7 @@
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>Security Control Center — managing agent access</t>
+          <t>Security Control Center - managing agent access</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
@@ -3330,10 +3402,10 @@
       </c>
       <c r="F13" s="14" t="inlineStr">
         <is>
-          <t>Relevant configuration evidence, but not needed for final chapter-specific synthesis.</t>
-        </is>
-      </c>
-      <c r="G13" s="14" t="n"/>
+          <t>Relevant configuration evidence that adds provider breadth without an independent deployment condition.</t>
+        </is>
+      </c>
+      <c r="G13" s="14" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
@@ -3363,10 +3435,10 @@
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>Relevant configuration evidence, but not needed for final chapter-specific synthesis.</t>
-        </is>
-      </c>
-      <c r="G14" s="14" t="n"/>
+          <t>Relevant configuration evidence that adds provider breadth without an independent deployment condition.</t>
+        </is>
+      </c>
+      <c r="G14" s="14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -3396,10 +3468,10 @@
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>Relevant governance evidence, but not needed for final chapter-specific synthesis.</t>
-        </is>
-      </c>
-      <c r="G15" s="14" t="n"/>
+          <t>Relevant governance evidence that adds provider breadth without an independent deployment condition.</t>
+        </is>
+      </c>
+      <c r="G15" s="14" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
@@ -3429,10 +3501,10 @@
       </c>
       <c r="F16" s="14" t="inlineStr">
         <is>
-          <t>Relevant governance evidence, but not needed for final chapter-specific synthesis.</t>
-        </is>
-      </c>
-      <c r="G16" s="14" t="n"/>
+          <t>Relevant governance evidence that adds provider breadth without an independent deployment condition.</t>
+        </is>
+      </c>
+      <c r="G16" s="14" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
@@ -3462,10 +3534,10 @@
       </c>
       <c r="F17" s="14" t="inlineStr">
         <is>
-          <t>Relevant sandbox/credential evidence, but not necessary once AWS/Anthropic evidence was retained.</t>
-        </is>
-      </c>
-      <c r="G17" s="14" t="n"/>
+          <t>Relevant sandbox evidence that adds provider breadth without an independent deployment condition.</t>
+        </is>
+      </c>
+      <c r="G17" s="14" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
@@ -3495,10 +3567,10 @@
       </c>
       <c r="F18" s="14" t="inlineStr">
         <is>
-          <t>Relevant supply-chain governance evidence, but not needed for selected subsection argument.</t>
-        </is>
-      </c>
-      <c r="G18" s="14" t="n"/>
+          <t>Relevant supply-chain governance evidence that adds provider breadth without an independent deployment condition.</t>
+        </is>
+      </c>
+      <c r="G18" s="14" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
@@ -3528,10 +3600,10 @@
       </c>
       <c r="F19" s="14" t="inlineStr">
         <is>
-          <t>Relevant policy/configuration evidence, but not needed for final chapter-specific synthesis.</t>
-        </is>
-      </c>
-      <c r="G19" s="14" t="n"/>
+          <t>Relevant policy evidence that adds provider breadth without an independent deployment condition.</t>
+        </is>
+      </c>
+      <c r="G19" s="14" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="14" t="inlineStr">
@@ -3561,10 +3633,10 @@
       </c>
       <c r="F20" s="14" t="inlineStr">
         <is>
-          <t>Relevant logging evidence, but not required by the final deployment-condition argument.</t>
-        </is>
-      </c>
-      <c r="G20" s="14" t="n"/>
+          <t>Relevant logging evidence that adds provider breadth without an independent deployment condition.</t>
+        </is>
+      </c>
+      <c r="G20" s="14" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
@@ -3594,10 +3666,10 @@
       </c>
       <c r="F21" s="14" t="inlineStr">
         <is>
-          <t>Relevant governance evidence, but not needed for final chapter-specific synthesis.</t>
-        </is>
-      </c>
-      <c r="G21" s="14" t="n"/>
+          <t>Relevant governance evidence that adds provider breadth without an independent deployment condition.</t>
+        </is>
+      </c>
+      <c r="G21" s="14" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="14" t="inlineStr">
@@ -3627,10 +3699,10 @@
       </c>
       <c r="F22" s="14" t="inlineStr">
         <is>
-          <t>Relevant governance evidence, but not needed for final chapter-specific synthesis.</t>
-        </is>
-      </c>
-      <c r="G22" s="14" t="n"/>
+          <t>Relevant governance evidence that adds provider breadth without an independent deployment condition.</t>
+        </is>
+      </c>
+      <c r="G22" s="14" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="14" t="inlineStr">
@@ -3660,10 +3732,10 @@
       </c>
       <c r="F23" s="14" t="inlineStr">
         <is>
-          <t>Relevant approval/authorization evidence, but not needed for final chapter-specific synthesis.</t>
-        </is>
-      </c>
-      <c r="G23" s="14" t="n"/>
+          <t>Relevant approval evidence that adds provider breadth without an independent deployment condition.</t>
+        </is>
+      </c>
+      <c r="G23" s="14" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="14" t="inlineStr">
@@ -3693,10 +3765,10 @@
       </c>
       <c r="F24" s="14" t="inlineStr">
         <is>
-          <t>Relevant role/permission evidence, but not needed for final chapter-specific synthesis.</t>
-        </is>
-      </c>
-      <c r="G24" s="14" t="n"/>
+          <t>Relevant role and permission evidence that adds provider breadth without an independent deployment condition.</t>
+        </is>
+      </c>
+      <c r="G24" s="14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3724,7 +3796,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="6" t="inlineStr">
         <is>
-          <t>Temp ref</t>
+          <t>Source ID</t>
         </is>
       </c>
       <c r="B1" s="6" t="inlineStr">
@@ -3761,7 +3833,7 @@
     <row r="2">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>[235]</t>
+          <t>TDES-ACA-001</t>
         </is>
       </c>
       <c r="B2" s="14" t="inlineStr">
@@ -3781,7 +3853,7 @@
       </c>
       <c r="E2" s="14" t="inlineStr">
         <is>
-          <t>Directly supports the selected credential-custody/supply-chain argument with non-redundant empirical evidence.</t>
+          <t>Provides source-native evidence on credential custody and skill supply chains.</t>
         </is>
       </c>
       <c r="F2" s="14" t="inlineStr">
@@ -3798,7 +3870,7 @@
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
-          <t>[236]</t>
+          <t>TDES-ACA-002</t>
         </is>
       </c>
       <c r="B3" s="14" t="inlineStr">
@@ -3818,7 +3890,7 @@
       </c>
       <c r="E3" s="14" t="inlineStr">
         <is>
-          <t>Directly supports the selected transitive-dependency/supply-chain-boundary argument and adds a distinct evidence function beyond credential leakage.</t>
+          <t>Provides source-native evidence on transitive dependencies and supply-chain boundaries.</t>
         </is>
       </c>
       <c r="F3" s="14" t="inlineStr">
@@ -3835,7 +3907,7 @@
     <row r="4">
       <c r="A4" s="14" t="inlineStr">
         <is>
-          <t>[238]</t>
+          <t>TDES-ACA-003</t>
         </is>
       </c>
       <c r="B4" s="14" t="inlineStr">
@@ -3845,22 +3917,22 @@
       </c>
       <c r="C4" s="14" t="inlineStr">
         <is>
-          <t>Human oversight of agentic systems in practice: Examining the oversight work, challenges, and heuristics of developers using software agents</t>
+          <t>Authenticated Delegation and Authorized AI Agents</t>
         </is>
       </c>
       <c r="D4" s="14" t="inlineStr">
         <is>
-          <t>human oversight; developer practice; workflow design</t>
+          <t>OAuth/OIDC; agent-specific credentials; delegation; scope</t>
         </is>
       </c>
       <c r="E4" s="14" t="inlineStr">
         <is>
-          <t>Directly supports the selected oversight-work taxonomy and complements existing direct-CUA human evidence without duplicating it.</t>
+          <t>Provides source-native evidence on agent-specific credentials delegated authority OAuth/OIDC and scope.</t>
         </is>
       </c>
       <c r="F4" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2606.05391</t>
+          <t>https://arxiv.org/abs/2501.09674</t>
         </is>
       </c>
       <c r="G4" s="14" t="inlineStr">
@@ -3872,7 +3944,7 @@
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>[237]</t>
+          <t>TDES-ACA-004</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
@@ -3882,22 +3954,22 @@
       </c>
       <c r="C5" s="14" t="inlineStr">
         <is>
-          <t>Authenticated Delegation and Authorized AI Agents</t>
+          <t>Human oversight of agentic systems in practice: Examining the oversight work, challenges, and heuristics of developers using software agents</t>
         </is>
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>OAuth/OIDC; agent-specific credentials; delegation; scope</t>
+          <t>human oversight; developer practice; workflow design</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
         <is>
-          <t>Directly supports the selected argument on agent-specific credentials, delegated authority, OAuth/OIDC, and scope; retained after full-text verification.</t>
+          <t>Provides source-native evidence on oversight work and developer workflow practice.</t>
         </is>
       </c>
       <c r="F5" s="14" t="inlineStr">
         <is>
-          <t>https://arxiv.org/abs/2501.09674</t>
+          <t>https://arxiv.org/abs/2606.05391</t>
         </is>
       </c>
       <c r="G5" s="14" t="inlineStr">
@@ -3909,7 +3981,7 @@
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>[243]</t>
+          <t>TDES-OFF-001</t>
         </is>
       </c>
       <c r="B6" s="14" t="inlineStr">
@@ -3919,7 +3991,7 @@
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>Anthropic — Beyond permission prompts: making Claude Code more secure and autonomous</t>
+          <t>Microsoft - Automate web and desktop apps with computer use</t>
         </is>
       </c>
       <c r="D6" s="14" t="inlineStr">
@@ -3929,12 +4001,12 @@
       </c>
       <c r="E6" s="14" t="inlineStr">
         <is>
-          <t>Directly supports the selected sandbox/approval-burden argument and provides source-reported operational evidence.</t>
+          <t>Documents credential semantics in a deployed computer-use setting.</t>
         </is>
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>https://www.anthropic.com/engineering/claude-code-sandboxing</t>
+          <t>https://learn.microsoft.com/en-us/microsoft-copilot-studio/computer-use</t>
         </is>
       </c>
       <c r="G6" s="14" t="inlineStr">
@@ -3946,7 +4018,7 @@
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>[239]</t>
+          <t>TDES-OFF-002</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
@@ -3956,7 +4028,7 @@
       </c>
       <c r="C7" s="14" t="inlineStr">
         <is>
-          <t>Microsoft — Automate web and desktop apps with computer use</t>
+          <t>Microsoft - Human supervision of computer use</t>
         </is>
       </c>
       <c r="D7" s="14" t="inlineStr">
@@ -3966,12 +4038,12 @@
       </c>
       <c r="E7" s="14" t="inlineStr">
         <is>
-          <t>Directly supports maker-provided versus end-user credential semantics in the deployed computer-use setting.</t>
+          <t>Documents human-supervision triggers and reliability conditions.</t>
         </is>
       </c>
       <c r="F7" s="14" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/microsoft-copilot-studio/computer-use</t>
+          <t>https://learn.microsoft.com/en-us/microsoft-copilot-studio/human-supervision-computer-use</t>
         </is>
       </c>
       <c r="G7" s="14" t="inlineStr">
@@ -3983,7 +4055,7 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>[240]</t>
+          <t>TDES-OFF-003</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
@@ -3993,7 +4065,7 @@
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>Microsoft — Human supervision of computer use</t>
+          <t>AWS - Security best practices for AgentCore Runtime</t>
         </is>
       </c>
       <c r="D8" s="14" t="inlineStr">
@@ -4003,12 +4075,12 @@
       </c>
       <c r="E8" s="14" t="inlineStr">
         <is>
-          <t>Directly supports the selected human-supervision trigger/reliability argument.</t>
+          <t>Documents delegated and autonomous credential handling and the microVM execution boundary.</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>https://learn.microsoft.com/en-us/microsoft-copilot-studio/human-supervision-computer-use</t>
+          <t>https://docs.aws.amazon.com/bedrock-agentcore/latest/devguide/runtime-security-best-practices.html</t>
         </is>
       </c>
       <c r="G8" s="14" t="inlineStr">
@@ -4020,7 +4092,7 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>[241]</t>
+          <t>TDES-OFF-004</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -4030,7 +4102,7 @@
       </c>
       <c r="C9" s="14" t="inlineStr">
         <is>
-          <t>AWS — Security best practices for AgentCore Runtime</t>
+          <t>AWS - Understanding Credentials Management in Amazon Bedrock AgentCore</t>
         </is>
       </c>
       <c r="D9" s="14" t="inlineStr">
@@ -4040,12 +4112,12 @@
       </c>
       <c r="E9" s="14" t="inlineStr">
         <is>
-          <t>Directly supports the selected user-delegated/autonomous credential and microVM execution-boundary argument.</t>
+          <t>Documents credential exposure and management inside a runtime boundary.</t>
         </is>
       </c>
       <c r="F9" s="14" t="inlineStr">
         <is>
-          <t>https://docs.aws.amazon.com/bedrock-agentcore/latest/devguide/runtime-security-best-practices.html</t>
+          <t>https://docs.aws.amazon.com/bedrock-agentcore/latest/devguide/security-credentials-management.html</t>
         </is>
       </c>
       <c r="G9" s="14" t="inlineStr">
@@ -4057,7 +4129,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>[242]</t>
+          <t>TDES-OFF-005</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -4067,7 +4139,7 @@
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>AWS — Understanding Credentials Management in Amazon Bedrock AgentCore</t>
+          <t>Anthropic - Beyond permission prompts: making Claude Code more secure and autonomous</t>
         </is>
       </c>
       <c r="D10" s="14" t="inlineStr">
@@ -4077,12 +4149,12 @@
       </c>
       <c r="E10" s="14" t="inlineStr">
         <is>
-          <t>Directly supports credential exposure/management inside the runtime boundary.</t>
+          <t>Documents sandboxing and approval-burden tradeoffs.</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>https://docs.aws.amazon.com/bedrock-agentcore/latest/devguide/security-credentials-management.html</t>
+          <t>https://www.anthropic.com/engineering/claude-code-sandboxing</t>
         </is>
       </c>
       <c r="G10" s="14" t="inlineStr">
@@ -4258,7 +4330,7 @@
       </c>
       <c r="G4" s="14" t="inlineStr">
         <is>
-          <t>Adjacent mechanism screened for chapter fit</t>
+          <t>Adjacent mechanism assessed for supplementary scope</t>
         </is>
       </c>
     </row>
@@ -4295,7 +4367,7 @@
       </c>
       <c r="G5" s="14" t="inlineStr">
         <is>
-          <t>Adjacent executable-skill evidence screened for chapter fit</t>
+          <t>Adjacent executable-skill evidence assessed for supplementary scope</t>
         </is>
       </c>
     </row>
@@ -5262,19 +5334,19 @@
       </c>
       <c r="B2" s="14" t="inlineStr">
         <is>
-          <t>Already in existing core corpus; deployment fields re-extracted; not a new TDES addition.</t>
+          <t>Already in the main corpus; deployment fields re-extracted; not a new TDES addition.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
-          <t>CHAPTER_FIT_NONREDUNDANT</t>
+          <t>NONREDUNDANT_EVIDENCE</t>
         </is>
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>Directly matches a predefined RQ4/Section 5 deployment-evidence gap and adds a non-redundant evidence function.</t>
+          <t>Independent source-native evidence on a deployment condition within the supplementary scope.</t>
         </is>
       </c>
     </row>
@@ -5286,19 +5358,19 @@
       </c>
       <c r="B4" s="14" t="inlineStr">
         <is>
-          <t>Relevant, but does not add a distinct source-native claim needed by the final Section 5 argument relative to retained evidence.</t>
+          <t>Relevant source that adds no independent deployment condition beyond retained evidence.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>OUTSIDE_FINAL_THEME</t>
+          <t>OUTSIDE_SUPPLEMENT_SCOPE</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>Relevant adjacent evidence, but its main contribution falls outside the deployment-condition claims actually synthesized in final Section 5.</t>
+          <t>Relevant adjacent evidence outside the defined supplementary deployment-evidence scope.</t>
         </is>
       </c>
     </row>
@@ -5310,7 +5382,7 @@
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>After the review cutoff and not required for the same-cutoff supplement.</t>
+          <t>Published after the review cutoff and excluded from the same-cutoff supplement.</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5394,7 @@
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>Eligible official deployment documentation that adds breadth rather than a distinct mechanism/configuration claim required by final Section 5.</t>
+          <t>Official deployment documentation that adds provider breadth but no independent deployment condition.</t>
         </is>
       </c>
     </row>
